--- a/data/datacall_template/00template/Eel_Data_Call_Annex0_Summary.xlsx
+++ b/data/datacall_template/00template/Eel_Data_Call_Annex0_Summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="readme" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="dropdown_tables" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="readme" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="dropdown_tables" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="104">
   <si>
     <r>
       <rPr>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t xml:space="preserve">contact email of the person responsible for providing the Annex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comment_funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you want, you can acknowledge here the funding</t>
   </si>
   <si>
     <t xml:space="preserve">comment</t>
@@ -474,32 +480,36 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -507,7 +517,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -515,7 +525,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -592,113 +602,227 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFFF0000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="201"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="201"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
+      <c r="A2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -713,281 +837,284 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF92D050"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="27.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="27.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="55.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="27.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="27.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="55.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="4" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="B2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="C2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="I3" s="9"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="8"/>
-      <c r="I4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="9"/>
+      <c r="I3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="8"/>
-      <c r="I5" s="9"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="C4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="8"/>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="I9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="I10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="F11" s="9"/>
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="C12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="I12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="I14" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="C13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="C14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="9"/>
+      <c r="I14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="C15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="I15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="I17" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="C16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="I16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="I18" s="9"/>
+      <c r="C17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="I17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="I18" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1011,7 +1138,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -1019,253 +1146,253 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="10"/>
+      <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="11"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="10"/>
+      <c r="A2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="11"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="10"/>
+      <c r="B3" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="11"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="10"/>
+      <c r="B4" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="10"/>
+      <c r="B5" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="10"/>
+      <c r="B6" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="10"/>
+      <c r="B7" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="10"/>
+      <c r="B8" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="10"/>
+      <c r="B9" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="10"/>
+      <c r="B10" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="10"/>
+      <c r="B11" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="10"/>
+      <c r="B12" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="10"/>
+      <c r="B13" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="10"/>
+      <c r="B14" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="10"/>
+      <c r="B15" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="10"/>
+      <c r="B16" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="10"/>
+      <c r="B17" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="10"/>
+      <c r="B18" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="10"/>
+      <c r="B19" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="10"/>
+      <c r="B20" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="10"/>
+      <c r="B21" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" s="10"/>
+      <c r="B22" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="10"/>
+      <c r="B23" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" s="10"/>
+      <c r="B24" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" s="10"/>
+      <c r="B25" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="10"/>
+      <c r="B26" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="10"/>
+      <c r="B27" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="10"/>
+      <c r="B28" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="10"/>
+      <c r="B29" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="10"/>
+      <c r="B30" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="10"/>
+      <c r="B31" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="10"/>
+      <c r="B32" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" s="10"/>
+      <c r="B33" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34" s="10"/>
+      <c r="B34" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C35" s="10"/>
+      <c r="B35" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" s="10"/>
+      <c r="B36" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" s="10"/>
+      <c r="B37" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="11"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C38" s="10"/>
+      <c r="B38" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="11"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C39" s="10"/>
+      <c r="B39" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C39" s="11"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C40" s="10"/>
+      <c r="B40" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="11"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C41" s="10"/>
+      <c r="C41" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/data/datacall_template/00template/Eel_Data_Call_Annex0_Summary.xlsx
+++ b/data/datacall_template/00template/Eel_Data_Call_Annex0_Summary.xlsx
@@ -122,7 +122,7 @@
     <t xml:space="preserve">comment_funding</t>
   </si>
   <si>
-    <t xml:space="preserve">If you want, you can acknowledge here the funding</t>
+    <t xml:space="preserve">Fill in funding source(s) (optional)</t>
   </si>
   <si>
     <t xml:space="preserve">comment</t>
